--- a/策划/Apex枪械数据-30赛季.xlsx
+++ b/策划/Apex枪械数据-30赛季.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\V\Desktop\简历\策划\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\V\Desktop\简历\Collection\策划\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D363125E-9CD3-4B87-9519-65B921AE906B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB2C644-A6E9-4002-85B5-B15F621840F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,7 +575,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>波塞科是复合弓，只能把子弹全部打空</t>
+    <t>波塞克是复合弓，只能把子弹全部打空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -666,31 +666,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -703,6 +679,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1001,155 +986,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6" t="s">
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="12" t="s">
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
     </row>
     <row r="2" spans="1:24" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="8" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="9" t="s">
+      <c r="N2" s="9"/>
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="12"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="10" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="11">
+      <c r="I3" s="9"/>
+      <c r="J3" s="1">
         <v>150</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="1">
         <v>175</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="1">
         <v>200</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="1">
         <v>225</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="10">
+      <c r="N3" s="9"/>
+      <c r="O3" s="3">
         <v>150</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="3">
         <v>175</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="3">
         <v>200</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="3">
         <v>225</v>
       </c>
-      <c r="S3" s="12"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="1">
         <v>14</v>
       </c>
@@ -1209,17 +1194,17 @@
         <f>TRUNC($D4*($N4/60))</f>
         <v>280</v>
       </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1239,10 +1224,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" ref="H5:H68" si="3">FLOOR(D5*G5,1)</f>
+        <f t="shared" ref="H5:H48" si="3">FLOOR(D5*G5,1)</f>
         <v>20</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="9" t="s">
         <v>108</v>
       </c>
       <c r="J5" s="1">
@@ -1284,15 +1269,15 @@
         <f t="shared" ref="S5:S48" si="4">TRUNC($D5*($N5/60))</f>
         <v>240</v>
       </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1313,7 +1298,7 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="9"/>
       <c r="J6" s="1">
         <f t="shared" ref="J6:M21" si="5">CEILING(J$3/$D6,1)</f>
         <v>10</v>
@@ -1334,7 +1319,7 @@
         <v>300</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" ref="O6:O68" si="6">(J6-1)*(60/$N6)</f>
+        <f t="shared" ref="O6:O48" si="6">(J6-1)*(60/$N6)</f>
         <v>1.8</v>
       </c>
       <c r="P6" s="3">
@@ -1353,11 +1338,11 @@
         <f>TRUNC($D6*($N6/60))</f>
         <v>80</v>
       </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -1421,24 +1406,24 @@
         <v>0.9</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" ref="R7:R68" si="9">(M7-1)*(60/$N7)</f>
+        <f t="shared" ref="R7:R48" si="9">(M7-1)*(60/$N7)</f>
         <v>1</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" si="4"/>
         <v>220</v>
       </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1461,7 +1446,7 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="9" t="s">
         <v>27</v>
       </c>
       <c r="J8" s="1">
@@ -1503,15 +1488,15 @@
         <f t="shared" si="4"/>
         <v>226</v>
       </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
@@ -1532,7 +1517,7 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="I9" s="4"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="1">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -1572,20 +1557,20 @@
         <f t="shared" si="4"/>
         <v>218</v>
       </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="1">
         <v>20</v>
       </c>
@@ -1645,17 +1630,17 @@
         <f t="shared" si="4"/>
         <v>224</v>
       </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1678,7 +1663,7 @@
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="9">
         <v>8</v>
       </c>
       <c r="J11" s="1">
@@ -1720,17 +1705,17 @@
         <f t="shared" si="4"/>
         <v>186</v>
       </c>
-      <c r="T11" s="5" t="s">
+      <c r="T11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1751,7 +1736,7 @@
         <f t="shared" si="3"/>
         <v>127</v>
       </c>
-      <c r="I12" s="4"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="1">
         <f t="shared" si="5"/>
         <v>2</v>
@@ -1791,11 +1776,11 @@
         <f t="shared" si="4"/>
         <v>73</v>
       </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
@@ -1866,17 +1851,17 @@
         <f t="shared" si="4"/>
         <v>178</v>
       </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="9">
         <v>8</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1899,7 +1884,7 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="9" t="s">
         <v>40</v>
       </c>
       <c r="J14" s="1">
@@ -1941,15 +1926,15 @@
         <f t="shared" si="4"/>
         <v>178</v>
       </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="1" t="s">
         <v>39</v>
       </c>
@@ -1970,7 +1955,7 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="I15" s="4"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="1">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -2010,20 +1995,20 @@
         <f t="shared" si="4"/>
         <v>158</v>
       </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>9</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="1">
         <v>14</v>
       </c>
@@ -2083,17 +2068,17 @@
         <f t="shared" si="4"/>
         <v>217</v>
       </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="9">
         <v>10</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2116,7 +2101,7 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="9" t="s">
         <v>46</v>
       </c>
       <c r="J17" s="1">
@@ -2158,15 +2143,15 @@
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
       <c r="C18" s="1" t="s">
         <v>45</v>
       </c>
@@ -2188,7 +2173,7 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="1">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -2228,17 +2213,17 @@
         <f t="shared" si="4"/>
         <v>214</v>
       </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="9">
         <v>11</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2303,15 +2288,15 @@
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="1" t="s">
         <v>48</v>
       </c>
@@ -2374,17 +2359,17 @@
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="9">
         <v>12</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2407,7 +2392,7 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="9" t="s">
         <v>53</v>
       </c>
       <c r="J21" s="1">
@@ -2449,15 +2434,15 @@
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
       <c r="C22" s="1" t="s">
         <v>52</v>
       </c>
@@ -2478,7 +2463,7 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="I22" s="4"/>
+      <c r="I22" s="9"/>
       <c r="J22" s="1">
         <f t="shared" ref="J22:M41" si="10">CEILING(J$3/$D22,1)</f>
         <v>7</v>
@@ -2503,11 +2488,11 @@
         <v>0.8</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" ref="P22:P68" si="11">(K22-1)*(60/$N22)</f>
+        <f t="shared" ref="P22:P48" si="11">(K22-1)*(60/$N22)</f>
         <v>0.93333333333333335</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" ref="Q22:Q68" si="12">(L22-1)*(60/$N22)</f>
+        <f t="shared" ref="Q22:Q48" si="12">(L22-1)*(60/$N22)</f>
         <v>1.0666666666666667</v>
       </c>
       <c r="R22" s="3">
@@ -2518,20 +2503,20 @@
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>13</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="1">
         <v>12</v>
       </c>
@@ -2591,17 +2576,17 @@
         <f t="shared" si="4"/>
         <v>216</v>
       </c>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="A24" s="9">
         <v>14</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2624,7 +2609,7 @@
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J24" s="1">
@@ -2666,15 +2651,15 @@
         <f t="shared" si="4"/>
         <v>145</v>
       </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
       <c r="C25" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,7 +2680,7 @@
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="I25" s="4"/>
+      <c r="I25" s="9"/>
       <c r="J25" s="1">
         <f t="shared" si="10"/>
         <v>6</v>
@@ -2735,20 +2720,20 @@
         <f t="shared" si="4"/>
         <v>188</v>
       </c>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>15</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="1">
         <v>15</v>
       </c>
@@ -2808,20 +2793,20 @@
         <f t="shared" si="4"/>
         <v>202</v>
       </c>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>16</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="1">
         <v>16</v>
       </c>
@@ -2881,20 +2866,20 @@
         <f t="shared" si="4"/>
         <v>208</v>
       </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>17</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="1">
         <v>21</v>
       </c>
@@ -2954,17 +2939,17 @@
         <f t="shared" si="4"/>
         <v>189</v>
       </c>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29" s="9">
         <v>18</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -3029,15 +3014,15 @@
         <f t="shared" si="4"/>
         <v>133</v>
       </c>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="1" t="s">
         <v>67</v>
       </c>
@@ -3100,17 +3085,17 @@
         <f t="shared" si="4"/>
         <v>133</v>
       </c>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31" s="9">
         <v>19</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -3175,15 +3160,15 @@
         <f t="shared" si="4"/>
         <v>192</v>
       </c>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="1" t="s">
         <v>67</v>
       </c>
@@ -3246,11 +3231,11 @@
         <f t="shared" si="4"/>
         <v>192</v>
       </c>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
@@ -3321,17 +3306,17 @@
         <f t="shared" si="4"/>
         <v>161</v>
       </c>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="A34" s="9">
         <v>21</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -3344,7 +3329,7 @@
         <v>0.85</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" ref="F34:F68" si="13">FLOOR(D34*E34,1)</f>
+        <f t="shared" ref="F34:F48" si="13">FLOOR(D34*E34,1)</f>
         <v>60</v>
       </c>
       <c r="G34" s="3">
@@ -3396,15 +3381,15 @@
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
       <c r="C35" s="1" t="s">
         <v>77</v>
       </c>
@@ -3467,17 +3452,17 @@
         <f t="shared" si="4"/>
         <v>130</v>
       </c>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="A36" s="9">
         <v>22</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="9" t="s">
         <v>78</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -3542,15 +3527,15 @@
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
       <c r="C37" s="1" t="s">
         <v>80</v>
       </c>
@@ -3614,20 +3599,20 @@
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>23</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="4"/>
+      <c r="C38" s="9"/>
       <c r="D38" s="1">
         <v>33</v>
       </c>
@@ -3687,11 +3672,11 @@
         <f t="shared" si="4"/>
         <v>135</v>
       </c>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -3762,17 +3747,17 @@
         <f t="shared" si="4"/>
         <v>125</v>
       </c>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40" s="9">
         <v>25</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -3795,7 +3780,7 @@
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="9" t="s">
         <v>88</v>
       </c>
       <c r="J40" s="1">
@@ -3837,15 +3822,15 @@
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
       <c r="C41" s="1" t="s">
         <v>87</v>
       </c>
@@ -3866,7 +3851,7 @@
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="I41" s="4"/>
+      <c r="I41" s="9"/>
       <c r="J41" s="1">
         <f t="shared" si="10"/>
         <v>3</v>
@@ -3906,17 +3891,17 @@
         <f t="shared" si="4"/>
         <v>117</v>
       </c>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42" s="9">
         <v>26</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -3939,7 +3924,7 @@
         <f t="shared" si="3"/>
         <v>135</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="9" t="s">
         <v>91</v>
       </c>
       <c r="J42" s="1">
@@ -3981,15 +3966,15 @@
         <f t="shared" si="4"/>
         <v>51</v>
       </c>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
       <c r="C43" s="1" t="s">
         <v>90</v>
       </c>
@@ -4010,7 +3995,7 @@
         <f t="shared" si="3"/>
         <v>81</v>
       </c>
-      <c r="I43" s="4"/>
+      <c r="I43" s="9"/>
       <c r="J43" s="1">
         <f t="shared" si="14"/>
         <v>4</v>
@@ -4050,11 +4035,11 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
@@ -4125,11 +4110,11 @@
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-      <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
@@ -4200,11 +4185,11 @@
         <f t="shared" si="4"/>
         <v>94</v>
       </c>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-      <c r="W45" s="4"/>
-      <c r="X45" s="4"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
@@ -4275,17 +4260,17 @@
         <f>TRUNC($D46*($N46/60))</f>
         <v>70</v>
       </c>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="4"/>
-      <c r="X46" s="4"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47" s="9">
         <v>30</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -4308,7 +4293,7 @@
         <f t="shared" si="3"/>
         <v>126</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="9" t="s">
         <v>92</v>
       </c>
       <c r="J47" s="1">
@@ -4350,15 +4335,15 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
       <c r="C48" s="1" t="s">
         <v>98</v>
       </c>
@@ -4379,9 +4364,9 @@
         <f t="shared" si="3"/>
         <v>158</v>
       </c>
-      <c r="I48" s="4"/>
+      <c r="I48" s="9"/>
       <c r="J48" s="1">
-        <f t="shared" ref="J48:M68" si="15">CEILING(J$3/$D48,1)</f>
+        <f t="shared" ref="J48:M48" si="15">CEILING(J$3/$D48,1)</f>
         <v>2</v>
       </c>
       <c r="K48" s="1">
@@ -4419,14 +4404,92 @@
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="102">
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="T14:X14"/>
+    <mergeCell ref="T15:X15"/>
+    <mergeCell ref="T16:X16"/>
+    <mergeCell ref="T7:X7"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="T1:X3"/>
+    <mergeCell ref="T4:X4"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="T11:X12"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="T23:X23"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="T17:X17"/>
+    <mergeCell ref="T18:X18"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="T21:X21"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="T8:X9"/>
@@ -4451,84 +4514,6 @@
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="T22:X22"/>
-    <mergeCell ref="T23:X23"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="T17:X17"/>
-    <mergeCell ref="T18:X18"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="T14:X14"/>
-    <mergeCell ref="T15:X15"/>
-    <mergeCell ref="T16:X16"/>
-    <mergeCell ref="T7:X7"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="T1:X3"/>
-    <mergeCell ref="T4:X4"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="T11:X12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="I42:I43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4553,152 +4538,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6" t="s">
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="12" t="s">
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
     </row>
     <row r="2" spans="1:24" ht="28" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="8" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="9" t="s">
+      <c r="N2" s="9"/>
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="12"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="10" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="11">
+      <c r="I3" s="9"/>
+      <c r="J3" s="1">
         <v>150</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="1">
         <v>175</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="1">
         <v>200</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="1">
         <v>225</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="10">
+      <c r="N3" s="9"/>
+      <c r="O3" s="3">
         <v>150</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="3">
         <v>175</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="3">
         <v>200</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="3">
         <v>225</v>
       </c>
-      <c r="S3" s="12"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="A4" s="9">
         <v>29</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -4721,7 +4706,7 @@
         <f t="shared" ref="H4:H5" si="1">FLOOR(D4*G4,1)</f>
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="9" t="s">
         <v>100</v>
       </c>
       <c r="J4" s="1">
@@ -4763,17 +4748,17 @@
         <f t="shared" ref="S4:S19" si="4">TRUNC($D4*($N4/60))</f>
         <v>190</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
       <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
@@ -4795,7 +4780,7 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -4835,23 +4820,23 @@
         <f t="shared" si="4"/>
         <v>230</v>
       </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="A6" s="9">
         <v>30</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="5">
         <v>18</v>
       </c>
       <c r="E6" s="3">
@@ -4868,7 +4853,7 @@
         <f t="shared" ref="H6:H19" si="6">FLOOR(D6*G6,1)</f>
         <v>22</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="9" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="1">
@@ -4910,19 +4895,19 @@
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="5">
         <f>14*2</f>
         <v>28</v>
       </c>
@@ -4940,7 +4925,7 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -4980,20 +4965,20 @@
         <f t="shared" si="4"/>
         <v>214</v>
       </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>29</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="1">
         <v>13</v>
       </c>
@@ -5053,23 +5038,23 @@
         <f t="shared" si="4"/>
         <v>234</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="T8" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="13">
+      <c r="C9" s="9"/>
+      <c r="D9" s="5">
         <v>12</v>
       </c>
       <c r="E9" s="3">
@@ -5128,20 +5113,20 @@
         <f t="shared" si="4"/>
         <v>216</v>
       </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>29</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="1">
         <v>17</v>
       </c>
@@ -5201,22 +5186,22 @@
         <f t="shared" si="4"/>
         <v>221</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="T10" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="1">
         <v>16</v>
       </c>
@@ -5276,11 +5261,11 @@
         <f t="shared" si="4"/>
         <v>208</v>
       </c>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -5351,13 +5336,13 @@
         <f t="shared" si="4"/>
         <v>169</v>
       </c>
-      <c r="T12" s="4" t="s">
+      <c r="T12" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
@@ -5369,7 +5354,7 @@
       <c r="C13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="5">
         <v>21</v>
       </c>
       <c r="E13" s="3">
@@ -5428,17 +5413,17 @@
         <f t="shared" si="4"/>
         <v>161</v>
       </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="9">
         <v>29</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -5503,17 +5488,17 @@
         <f t="shared" si="4"/>
         <v>105</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="1" t="s">
         <v>77</v>
       </c>
@@ -5576,23 +5561,23 @@
         <f t="shared" si="4"/>
         <v>130</v>
       </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="9">
         <v>30</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="6">
         <v>71</v>
       </c>
       <c r="E16" s="3">
@@ -5651,15 +5636,15 @@
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="1" t="s">
         <v>77</v>
       </c>
@@ -5722,11 +5707,11 @@
         <f t="shared" si="4"/>
         <v>130</v>
       </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -5797,23 +5782,23 @@
         <f t="shared" si="4"/>
         <v>151</v>
       </c>
-      <c r="T18" s="4" t="s">
+      <c r="T18" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>30</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="13">
+      <c r="C19" s="9"/>
+      <c r="D19" s="5">
         <v>33</v>
       </c>
       <c r="E19" s="3">
@@ -5872,47 +5857,47 @@
         <f t="shared" si="4"/>
         <v>135</v>
       </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C3"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="T1:X3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="N1:N3"/>
     <mergeCell ref="T18:X19"/>
     <mergeCell ref="T4:X7"/>
     <mergeCell ref="T8:X9"/>
     <mergeCell ref="T10:X11"/>
     <mergeCell ref="T12:X13"/>
     <mergeCell ref="T14:X17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="T1:X3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C3"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:N3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5931,7 +5916,7 @@
     <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13.08203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="16"/>
+    <col min="8" max="8" width="8.6640625" style="8"/>
     <col min="9" max="9" width="8.6640625" style="1"/>
     <col min="10" max="11" width="20.58203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.1640625" style="1" customWidth="1"/>
@@ -5939,94 +5924,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="1">
         <f>ttk_dfs!D4</f>
         <v>14</v>
@@ -6042,7 +6027,7 @@
         <f>FLOOR((D4*E4-200)/D4,1)</f>
         <v>158</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="8">
         <f>G4/E4</f>
         <v>0.91329479768786126</v>
       </c>
@@ -6063,10 +6048,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -6087,7 +6072,7 @@
         <f t="shared" ref="G5:G48" si="0">FLOOR((D5*E5-200)/D5,1)</f>
         <v>35</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="8">
         <f t="shared" ref="H5:H48" si="1">G5/E5</f>
         <v>0.72916666666666663</v>
       </c>
@@ -6108,8 +6093,8 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
@@ -6128,7 +6113,7 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="8">
         <f t="shared" si="1"/>
         <v>0.72916666666666663</v>
       </c>
@@ -6173,7 +6158,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="8">
         <f t="shared" si="1"/>
         <v>0.6428571428571429</v>
       </c>
@@ -6194,10 +6179,10 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -6218,7 +6203,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="8">
         <f t="shared" si="1"/>
         <v>0.65714285714285714</v>
       </c>
@@ -6239,8 +6224,8 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
@@ -6259,7 +6244,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="8">
         <f t="shared" si="1"/>
         <v>0.62857142857142856</v>
       </c>
@@ -6283,10 +6268,10 @@
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="1">
         <f>ttk_dfs!D10</f>
         <v>20</v>
@@ -6302,7 +6287,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="8">
         <f t="shared" si="1"/>
         <v>0.65517241379310343</v>
       </c>
@@ -6323,10 +6308,10 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -6347,7 +6332,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="8">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -6368,8 +6353,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
@@ -6388,7 +6373,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="8">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
@@ -6433,7 +6418,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="8">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -6454,10 +6439,10 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="9">
         <v>8</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -6478,7 +6463,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="8">
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
@@ -6499,8 +6484,8 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
@@ -6519,7 +6504,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="8">
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
@@ -6543,10 +6528,10 @@
       <c r="A16" s="1">
         <v>9</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="1">
         <f>ttk_dfs!D16</f>
         <v>14</v>
@@ -6562,7 +6547,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="8">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -6583,10 +6568,10 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="9">
         <v>10</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -6607,7 +6592,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="8">
         <f t="shared" si="1"/>
         <v>0.53846153846153844</v>
       </c>
@@ -6628,9 +6613,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="15" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="1">
@@ -6648,7 +6633,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="8">
         <f t="shared" si="1"/>
         <v>0.69230769230769229</v>
       </c>
@@ -6669,10 +6654,10 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="9">
         <v>11</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -6693,7 +6678,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="8">
         <f t="shared" si="1"/>
         <v>0.65517241379310343</v>
       </c>
@@ -6714,8 +6699,8 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="1" t="s">
         <v>48</v>
       </c>
@@ -6734,7 +6719,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="8">
         <f t="shared" si="1"/>
         <v>0.67741935483870963</v>
       </c>
@@ -6755,10 +6740,10 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="9">
         <v>12</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -6779,7 +6764,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="8">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -6800,8 +6785,8 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
       <c r="C22" s="1" t="s">
         <v>52</v>
       </c>
@@ -6820,7 +6805,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="8">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -6844,10 +6829,10 @@
       <c r="A23" s="1">
         <v>13</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="1">
         <f>ttk_dfs!D23</f>
         <v>12</v>
@@ -6863,7 +6848,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="8">
         <f t="shared" si="1"/>
         <v>0.37037037037037035</v>
       </c>
@@ -6884,10 +6869,10 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="A24" s="9">
         <v>14</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -6908,7 +6893,7 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="8">
         <f t="shared" si="1"/>
         <v>0.82499999999999996</v>
       </c>
@@ -6929,8 +6914,8 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
       <c r="C25" s="1" t="s">
         <v>57</v>
       </c>
@@ -6949,7 +6934,7 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="8">
         <f t="shared" si="1"/>
         <v>0.82499999999999996</v>
       </c>
@@ -6973,10 +6958,10 @@
       <c r="A26" s="1">
         <v>15</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="1">
         <f>ttk_dfs!D26</f>
         <v>15</v>
@@ -6992,7 +6977,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="8">
         <f t="shared" si="1"/>
         <v>0.54838709677419351</v>
       </c>
@@ -7016,10 +7001,10 @@
       <c r="A27" s="1">
         <v>16</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="1">
         <f>ttk_dfs!D27</f>
         <v>16</v>
@@ -7035,7 +7020,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="8">
         <f t="shared" si="1"/>
         <v>0.45833333333333331</v>
       </c>
@@ -7059,10 +7044,10 @@
       <c r="A28" s="1">
         <v>17</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="1">
         <f>ttk_dfs!D28</f>
         <v>21</v>
@@ -7078,7 +7063,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="8">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
@@ -7099,10 +7084,10 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29" s="9">
         <v>18</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="9" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -7123,7 +7108,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="8">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -7144,8 +7129,8 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="1" t="s">
         <v>67</v>
       </c>
@@ -7164,7 +7149,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="8">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7185,10 +7170,10 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31" s="9">
         <v>19</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -7209,7 +7194,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="8">
         <f t="shared" si="1"/>
         <v>0.51851851851851849</v>
       </c>
@@ -7230,8 +7215,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="1" t="s">
         <v>67</v>
       </c>
@@ -7250,7 +7235,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="8">
         <f t="shared" si="1"/>
         <v>0.55172413793103448</v>
       </c>
@@ -7295,7 +7280,7 @@
         <f>FLOOR((D33*E33-200)/D33,1)</f>
         <v>15</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="8">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7316,10 +7301,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="A34" s="9">
         <v>21</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -7340,7 +7325,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="8">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
@@ -7361,8 +7346,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
       <c r="C35" s="1" t="s">
         <v>77</v>
       </c>
@@ -7381,7 +7366,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="8">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7402,10 +7387,10 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="A36" s="9">
         <v>22</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="9" t="s">
         <v>78</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -7426,7 +7411,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="8">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -7445,17 +7430,17 @@
         <f t="shared" si="3"/>
         <v>30.857142857142854</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="M36" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
       <c r="C37" s="1" t="s">
         <v>80</v>
       </c>
@@ -7474,7 +7459,7 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="8">
         <f t="shared" si="1"/>
         <v>0.92500000000000004</v>
       </c>
@@ -7493,20 +7478,20 @@
         <f t="shared" si="3"/>
         <v>31.714285714285708</v>
       </c>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>23</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="4"/>
+      <c r="C38" s="9"/>
       <c r="D38" s="1">
         <f>ttk_dfs!D38</f>
         <v>33</v>
@@ -7522,7 +7507,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="8">
         <f t="shared" si="1"/>
         <v>0.5625</v>
       </c>
@@ -7567,7 +7552,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="8">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
@@ -7588,10 +7573,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40" s="9">
         <v>25</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -7612,7 +7597,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="8">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7633,8 +7618,8 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
       <c r="C41" s="1" t="s">
         <v>87</v>
       </c>
@@ -7653,7 +7638,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="8">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7674,10 +7659,10 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42" s="9">
         <v>26</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -7698,7 +7683,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="8">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -7719,8 +7704,8 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
       <c r="C43" s="1" t="s">
         <v>90</v>
       </c>
@@ -7739,7 +7724,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H43" s="8">
         <f t="shared" si="1"/>
         <v>0.44444444444444442</v>
       </c>
@@ -7784,7 +7769,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="8">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -7829,7 +7814,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H45" s="16">
+      <c r="H45" s="8">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
@@ -7874,7 +7859,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H46" s="16">
+      <c r="H46" s="8">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -7895,10 +7880,10 @@
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47" s="9">
         <v>30</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -7919,7 +7904,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H47" s="8">
         <f t="shared" si="1"/>
         <v>0.5714285714285714</v>
       </c>
@@ -7940,8 +7925,8 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
       <c r="C48" s="1" t="s">
         <v>98</v>
       </c>
@@ -7960,7 +7945,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="8">
         <f t="shared" si="1"/>
         <v>0.5714285714285714</v>
       </c>
@@ -7982,18 +7967,29 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="M1:Q3"/>
-    <mergeCell ref="M36:Q37"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="G1:G3"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="L1:L3"/>
-    <mergeCell ref="K1:K3"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:C3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:B30"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="A5:A6"/>
@@ -8010,29 +8006,18 @@
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:C3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="M1:Q3"/>
+    <mergeCell ref="M36:Q37"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="G1:G3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="L1:L3"/>
+    <mergeCell ref="K1:K3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
